--- a/src/lib/SHOP NX2 ONLINE LIST.xlsx
+++ b/src/lib/SHOP NX2 ONLINE LIST.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9B43BA9-D43C-AA40-91D8-CC639AB16B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="7755"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="7755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -504,7 +505,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -673,33 +674,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -718,10 +692,37 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -742,9 +743,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -782,9 +783,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -819,7 +820,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -854,7 +855,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1027,42 +1028,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G354"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" style="19" customWidth="1"/>
-    <col min="3" max="3" width="6.5703125" style="1" customWidth="1"/>
-    <col min="4" max="5" width="6.7109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="6.859375" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.45703125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="6.58984375" style="1" customWidth="1"/>
+    <col min="4" max="5" width="6.72265625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.14453125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:7" ht="31.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="12" t="s">
+      <c r="D2" s="13"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="G2" s="12"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G2" s="13"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1075,7 +1076,7 @@
       <c r="D3" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="7" t="s">
         <v>76</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -1085,7 +1086,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1098,7 +1099,7 @@
       <c r="D4" s="2">
         <v>400</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="7">
         <v>900</v>
       </c>
       <c r="F4" s="2">
@@ -1108,7 +1109,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1121,7 +1122,7 @@
       <c r="D5" s="2">
         <v>400</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="7">
         <v>900</v>
       </c>
       <c r="F5" s="2">
@@ -1131,7 +1132,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1144,7 +1145,7 @@
       <c r="D6" s="2">
         <v>400</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="7">
         <v>900</v>
       </c>
       <c r="F6" s="2">
@@ -1154,7 +1155,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -1167,7 +1168,7 @@
       <c r="D7" s="2">
         <v>400</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="7">
         <v>900</v>
       </c>
       <c r="F7" s="2">
@@ -1177,7 +1178,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -1190,7 +1191,7 @@
       <c r="D8" s="2">
         <v>400</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="7">
         <v>900</v>
       </c>
       <c r="F8" s="2">
@@ -1200,7 +1201,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -1213,7 +1214,7 @@
       <c r="D9" s="2">
         <v>400</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="7">
         <v>900</v>
       </c>
       <c r="F9" s="2">
@@ -1223,7 +1224,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>7</v>
       </c>
@@ -1236,7 +1237,7 @@
       <c r="D10" s="2">
         <v>400</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="7">
         <v>900</v>
       </c>
       <c r="F10" s="2">
@@ -1246,7 +1247,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -1259,7 +1260,7 @@
       <c r="D11" s="2">
         <v>400</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="7">
         <v>900</v>
       </c>
       <c r="F11" s="2">
@@ -1269,7 +1270,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>9</v>
       </c>
@@ -1282,7 +1283,7 @@
       <c r="D12" s="2">
         <v>400</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="7">
         <v>900</v>
       </c>
       <c r="F12" s="2">
@@ -1292,7 +1293,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>10</v>
       </c>
@@ -1305,7 +1306,7 @@
       <c r="D13" s="2">
         <v>400</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="7">
         <v>900</v>
       </c>
       <c r="F13" s="2">
@@ -1315,7 +1316,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>11</v>
       </c>
@@ -1328,7 +1329,7 @@
       <c r="D14" s="2">
         <v>400</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="7">
         <v>900</v>
       </c>
       <c r="F14" s="2">
@@ -1338,7 +1339,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>12</v>
       </c>
@@ -1351,7 +1352,7 @@
       <c r="D15" s="2">
         <v>400</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="7">
         <v>900</v>
       </c>
       <c r="F15" s="2">
@@ -1361,7 +1362,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>13</v>
       </c>
@@ -1374,7 +1375,7 @@
       <c r="D16" s="2">
         <v>400</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="7">
         <v>900</v>
       </c>
       <c r="F16" s="2">
@@ -1384,7 +1385,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>14</v>
       </c>
@@ -1397,7 +1398,7 @@
       <c r="D17" s="2">
         <v>400</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="7">
         <v>900</v>
       </c>
       <c r="F17" s="2">
@@ -1407,7 +1408,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>15</v>
       </c>
@@ -1420,7 +1421,7 @@
       <c r="D18" s="2">
         <v>400</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="7">
         <v>900</v>
       </c>
       <c r="F18" s="2">
@@ -1430,7 +1431,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -1443,7 +1444,7 @@
       <c r="D19" s="2">
         <v>400</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="7">
         <v>900</v>
       </c>
       <c r="F19" s="2">
@@ -1453,7 +1454,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>17</v>
       </c>
@@ -1466,7 +1467,7 @@
       <c r="D20" s="2">
         <v>400</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="7">
         <v>900</v>
       </c>
       <c r="F20" s="2">
@@ -1476,7 +1477,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>18</v>
       </c>
@@ -1489,7 +1490,7 @@
       <c r="D21" s="2">
         <v>400</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="7">
         <v>900</v>
       </c>
       <c r="F21" s="2">
@@ -1499,7 +1500,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>19</v>
       </c>
@@ -1512,7 +1513,7 @@
       <c r="D22" s="2">
         <v>400</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="7">
         <v>900</v>
       </c>
       <c r="F22" s="2">
@@ -1522,7 +1523,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>20</v>
       </c>
@@ -1535,7 +1536,7 @@
       <c r="D23" s="2">
         <v>400</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="7">
         <v>900</v>
       </c>
       <c r="F23" s="2">
@@ -1545,7 +1546,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>21</v>
       </c>
@@ -1558,7 +1559,7 @@
       <c r="D24" s="2">
         <v>400</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="7">
         <v>900</v>
       </c>
       <c r="F24" s="2">
@@ -1568,7 +1569,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>22</v>
       </c>
@@ -1581,7 +1582,7 @@
       <c r="D25" s="2">
         <v>400</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="7">
         <v>900</v>
       </c>
       <c r="F25" s="2">
@@ -1591,7 +1592,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>23</v>
       </c>
@@ -1604,7 +1605,7 @@
       <c r="D26" s="2">
         <v>400</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="7">
         <v>900</v>
       </c>
       <c r="F26" s="2">
@@ -1614,7 +1615,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>24</v>
       </c>
@@ -1627,7 +1628,7 @@
       <c r="D27" s="2">
         <v>400</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="7">
         <v>900</v>
       </c>
       <c r="F27" s="2">
@@ -1637,7 +1638,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>25</v>
       </c>
@@ -1650,7 +1651,7 @@
       <c r="D28" s="2">
         <v>400</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="7">
         <v>900</v>
       </c>
       <c r="F28" s="2">
@@ -1660,7 +1661,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>26</v>
       </c>
@@ -1673,7 +1674,7 @@
       <c r="D29" s="2">
         <v>400</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="7">
         <v>900</v>
       </c>
       <c r="F29" s="2">
@@ -1683,7 +1684,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>27</v>
       </c>
@@ -1696,7 +1697,7 @@
       <c r="D30" s="2">
         <v>400</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="7">
         <v>900</v>
       </c>
       <c r="F30" s="2">
@@ -1706,7 +1707,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>28</v>
       </c>
@@ -1719,7 +1720,7 @@
       <c r="D31" s="2">
         <v>400</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="7">
         <v>900</v>
       </c>
       <c r="F31" s="2">
@@ -1729,7 +1730,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>29</v>
       </c>
@@ -1742,7 +1743,7 @@
       <c r="D32" s="2">
         <v>400</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="7">
         <v>900</v>
       </c>
       <c r="F32" s="2">
@@ -1752,7 +1753,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>30</v>
       </c>
@@ -1765,7 +1766,7 @@
       <c r="D33" s="2">
         <v>400</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="7">
         <v>900</v>
       </c>
       <c r="F33" s="2">
@@ -1775,7 +1776,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>31</v>
       </c>
@@ -1788,7 +1789,7 @@
       <c r="D34" s="2">
         <v>400</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="7">
         <v>900</v>
       </c>
       <c r="F34" s="2">
@@ -1798,7 +1799,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>32</v>
       </c>
@@ -1811,7 +1812,7 @@
       <c r="D35" s="2">
         <v>400</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="7">
         <v>900</v>
       </c>
       <c r="F35" s="2">
@@ -1821,7 +1822,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>33</v>
       </c>
@@ -1834,7 +1835,7 @@
       <c r="D36" s="2">
         <v>400</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="7">
         <v>900</v>
       </c>
       <c r="F36" s="2">
@@ -1844,7 +1845,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>34</v>
       </c>
@@ -1857,7 +1858,7 @@
       <c r="D37" s="2">
         <v>400</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37" s="7">
         <v>900</v>
       </c>
       <c r="F37" s="2">
@@ -1867,7 +1868,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>35</v>
       </c>
@@ -1880,7 +1881,7 @@
       <c r="D38" s="2">
         <v>400</v>
       </c>
-      <c r="E38" s="16">
+      <c r="E38" s="7">
         <v>900</v>
       </c>
       <c r="F38" s="2">
@@ -1890,7 +1891,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>36</v>
       </c>
@@ -1903,7 +1904,7 @@
       <c r="D39" s="2">
         <v>400</v>
       </c>
-      <c r="E39" s="16">
+      <c r="E39" s="7">
         <v>900</v>
       </c>
       <c r="F39" s="2">
@@ -1913,7 +1914,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>37</v>
       </c>
@@ -1926,7 +1927,7 @@
       <c r="D40" s="2">
         <v>400</v>
       </c>
-      <c r="E40" s="16">
+      <c r="E40" s="7">
         <v>900</v>
       </c>
       <c r="F40" s="2">
@@ -1936,7 +1937,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>38</v>
       </c>
@@ -1949,7 +1950,7 @@
       <c r="D41" s="2">
         <v>400</v>
       </c>
-      <c r="E41" s="16">
+      <c r="E41" s="7">
         <v>900</v>
       </c>
       <c r="F41" s="2">
@@ -1959,7 +1960,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>39</v>
       </c>
@@ -1972,7 +1973,7 @@
       <c r="D42" s="2">
         <v>400</v>
       </c>
-      <c r="E42" s="16">
+      <c r="E42" s="7">
         <v>900</v>
       </c>
       <c r="F42" s="2">
@@ -1982,7 +1983,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>40</v>
       </c>
@@ -1995,7 +1996,7 @@
       <c r="D43" s="2">
         <v>400</v>
       </c>
-      <c r="E43" s="16">
+      <c r="E43" s="7">
         <v>900</v>
       </c>
       <c r="F43" s="2">
@@ -2005,7 +2006,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>41</v>
       </c>
@@ -2018,7 +2019,7 @@
       <c r="D44" s="2">
         <v>400</v>
       </c>
-      <c r="E44" s="16">
+      <c r="E44" s="7">
         <v>900</v>
       </c>
       <c r="F44" s="2">
@@ -2028,7 +2029,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>42</v>
       </c>
@@ -2041,7 +2042,7 @@
       <c r="D45" s="2">
         <v>400</v>
       </c>
-      <c r="E45" s="16">
+      <c r="E45" s="7">
         <v>900</v>
       </c>
       <c r="F45" s="2">
@@ -2051,7 +2052,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>43</v>
       </c>
@@ -2064,7 +2065,7 @@
       <c r="D46" s="2">
         <v>400</v>
       </c>
-      <c r="E46" s="16">
+      <c r="E46" s="7">
         <v>900</v>
       </c>
       <c r="F46" s="2">
@@ -2074,7 +2075,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>44</v>
       </c>
@@ -2087,7 +2088,7 @@
       <c r="D47" s="2">
         <v>400</v>
       </c>
-      <c r="E47" s="16">
+      <c r="E47" s="7">
         <v>900</v>
       </c>
       <c r="F47" s="2">
@@ -2097,7 +2098,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>45</v>
       </c>
@@ -2110,7 +2111,7 @@
       <c r="D48" s="2">
         <v>400</v>
       </c>
-      <c r="E48" s="16">
+      <c r="E48" s="7">
         <v>900</v>
       </c>
       <c r="F48" s="2">
@@ -2120,7 +2121,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>46</v>
       </c>
@@ -2133,7 +2134,7 @@
       <c r="D49" s="2">
         <v>400</v>
       </c>
-      <c r="E49" s="16">
+      <c r="E49" s="7">
         <v>900</v>
       </c>
       <c r="F49" s="2">
@@ -2143,7 +2144,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>47</v>
       </c>
@@ -2156,7 +2157,7 @@
       <c r="D50" s="2">
         <v>400</v>
       </c>
-      <c r="E50" s="16">
+      <c r="E50" s="7">
         <v>900</v>
       </c>
       <c r="F50" s="2">
@@ -2166,7 +2167,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>48</v>
       </c>
@@ -2179,7 +2180,7 @@
       <c r="D51" s="2">
         <v>400</v>
       </c>
-      <c r="E51" s="16">
+      <c r="E51" s="7">
         <v>900</v>
       </c>
       <c r="F51" s="2">
@@ -2189,7 +2190,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>49</v>
       </c>
@@ -2202,7 +2203,7 @@
       <c r="D52" s="2">
         <v>400</v>
       </c>
-      <c r="E52" s="16">
+      <c r="E52" s="7">
         <v>900</v>
       </c>
       <c r="F52" s="2">
@@ -2212,7 +2213,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>50</v>
       </c>
@@ -2225,7 +2226,7 @@
       <c r="D53" s="2">
         <v>400</v>
       </c>
-      <c r="E53" s="16">
+      <c r="E53" s="7">
         <v>900</v>
       </c>
       <c r="F53" s="2">
@@ -2235,7 +2236,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>51</v>
       </c>
@@ -2248,7 +2249,7 @@
       <c r="D54" s="2">
         <v>400</v>
       </c>
-      <c r="E54" s="16">
+      <c r="E54" s="7">
         <v>900</v>
       </c>
       <c r="F54" s="2">
@@ -2258,7 +2259,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>52</v>
       </c>
@@ -2271,7 +2272,7 @@
       <c r="D55" s="2">
         <v>400</v>
       </c>
-      <c r="E55" s="16">
+      <c r="E55" s="7">
         <v>900</v>
       </c>
       <c r="F55" s="2">
@@ -2281,7 +2282,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>53</v>
       </c>
@@ -2294,7 +2295,7 @@
       <c r="D56" s="2">
         <v>400</v>
       </c>
-      <c r="E56" s="16">
+      <c r="E56" s="7">
         <v>900</v>
       </c>
       <c r="F56" s="2">
@@ -2304,7 +2305,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>54</v>
       </c>
@@ -2317,7 +2318,7 @@
       <c r="D57" s="2">
         <v>400</v>
       </c>
-      <c r="E57" s="16">
+      <c r="E57" s="7">
         <v>900</v>
       </c>
       <c r="F57" s="2">
@@ -2327,7 +2328,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>55</v>
       </c>
@@ -2340,7 +2341,7 @@
       <c r="D58" s="2">
         <v>400</v>
       </c>
-      <c r="E58" s="16">
+      <c r="E58" s="7">
         <v>900</v>
       </c>
       <c r="F58" s="2">
@@ -2350,7 +2351,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>56</v>
       </c>
@@ -2363,7 +2364,7 @@
       <c r="D59" s="2">
         <v>400</v>
       </c>
-      <c r="E59" s="16">
+      <c r="E59" s="7">
         <v>900</v>
       </c>
       <c r="F59" s="2">
@@ -2373,7 +2374,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>57</v>
       </c>
@@ -2386,7 +2387,7 @@
       <c r="D60" s="2">
         <v>400</v>
       </c>
-      <c r="E60" s="16">
+      <c r="E60" s="7">
         <v>900</v>
       </c>
       <c r="F60" s="2">
@@ -2396,7 +2397,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>58</v>
       </c>
@@ -2409,7 +2410,7 @@
       <c r="D61" s="2">
         <v>400</v>
       </c>
-      <c r="E61" s="16">
+      <c r="E61" s="7">
         <v>900</v>
       </c>
       <c r="F61" s="2">
@@ -2419,7 +2420,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>59</v>
       </c>
@@ -2432,7 +2433,7 @@
       <c r="D62" s="2">
         <v>400</v>
       </c>
-      <c r="E62" s="16">
+      <c r="E62" s="7">
         <v>900</v>
       </c>
       <c r="F62" s="2">
@@ -2442,7 +2443,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>60</v>
       </c>
@@ -2455,7 +2456,7 @@
       <c r="D63" s="2">
         <v>400</v>
       </c>
-      <c r="E63" s="16">
+      <c r="E63" s="7">
         <v>900</v>
       </c>
       <c r="F63" s="2">
@@ -2465,7 +2466,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>61</v>
       </c>
@@ -2478,7 +2479,7 @@
       <c r="D64" s="2">
         <v>400</v>
       </c>
-      <c r="E64" s="16">
+      <c r="E64" s="7">
         <v>900</v>
       </c>
       <c r="F64" s="2">
@@ -2488,7 +2489,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>62</v>
       </c>
@@ -2501,7 +2502,7 @@
       <c r="D65" s="2">
         <v>400</v>
       </c>
-      <c r="E65" s="16">
+      <c r="E65" s="7">
         <v>900</v>
       </c>
       <c r="F65" s="2">
@@ -2511,7 +2512,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <v>63</v>
       </c>
@@ -2524,7 +2525,7 @@
       <c r="D66" s="2">
         <v>400</v>
       </c>
-      <c r="E66" s="16">
+      <c r="E66" s="7">
         <v>900</v>
       </c>
       <c r="F66" s="2">
@@ -2534,7 +2535,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>64</v>
       </c>
@@ -2547,7 +2548,7 @@
       <c r="D67" s="2">
         <v>400</v>
       </c>
-      <c r="E67" s="16">
+      <c r="E67" s="7">
         <v>900</v>
       </c>
       <c r="F67" s="2">
@@ -2557,16 +2558,16 @@
         <v>250</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="21"/>
-      <c r="B68" s="21"/>
+    <row r="68" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="12"/>
+      <c r="B68" s="12"/>
       <c r="C68" s="2">
         <v>250</v>
       </c>
       <c r="D68" s="2">
         <v>400</v>
       </c>
-      <c r="E68" s="16">
+      <c r="E68" s="7">
         <v>900</v>
       </c>
       <c r="F68" s="2">
@@ -2576,16 +2577,16 @@
         <v>250</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="21"/>
-      <c r="B69" s="21"/>
+    <row r="69" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="12"/>
+      <c r="B69" s="12"/>
       <c r="C69" s="2">
         <v>250</v>
       </c>
       <c r="D69" s="2">
         <v>400</v>
       </c>
-      <c r="E69" s="16">
+      <c r="E69" s="7">
         <v>900</v>
       </c>
       <c r="F69" s="2">
@@ -2595,16 +2596,16 @@
         <v>250</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="21"/>
-      <c r="B70" s="21"/>
+    <row r="70" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="12"/>
+      <c r="B70" s="12"/>
       <c r="C70" s="2">
         <v>250</v>
       </c>
       <c r="D70" s="2">
         <v>400</v>
       </c>
-      <c r="E70" s="16">
+      <c r="E70" s="7">
         <v>900</v>
       </c>
       <c r="F70" s="2">
@@ -2614,16 +2615,16 @@
         <v>250</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="21"/>
-      <c r="B71" s="21"/>
+    <row r="71" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="12"/>
+      <c r="B71" s="12"/>
       <c r="C71" s="2">
         <v>250</v>
       </c>
       <c r="D71" s="2">
         <v>400</v>
       </c>
-      <c r="E71" s="16">
+      <c r="E71" s="7">
         <v>900</v>
       </c>
       <c r="F71" s="2">
@@ -2633,16 +2634,16 @@
         <v>250</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="21"/>
-      <c r="B72" s="21"/>
+    <row r="72" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="12"/>
+      <c r="B72" s="12"/>
       <c r="C72" s="2">
         <v>250</v>
       </c>
       <c r="D72" s="2">
         <v>400</v>
       </c>
-      <c r="E72" s="16">
+      <c r="E72" s="7">
         <v>900</v>
       </c>
       <c r="F72" s="2">
@@ -2652,16 +2653,16 @@
         <v>250</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="21"/>
-      <c r="B73" s="21"/>
+    <row r="73" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="12"/>
+      <c r="B73" s="12"/>
       <c r="C73" s="2">
         <v>250</v>
       </c>
       <c r="D73" s="2">
         <v>400</v>
       </c>
-      <c r="E73" s="16">
+      <c r="E73" s="7">
         <v>900</v>
       </c>
       <c r="F73" s="2">
@@ -2671,16 +2672,16 @@
         <v>250</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="21"/>
-      <c r="B74" s="21"/>
+    <row r="74" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="12"/>
+      <c r="B74" s="12"/>
       <c r="C74" s="2">
         <v>250</v>
       </c>
       <c r="D74" s="2">
         <v>400</v>
       </c>
-      <c r="E74" s="16">
+      <c r="E74" s="7">
         <v>900</v>
       </c>
       <c r="F74" s="2">
@@ -2690,16 +2691,16 @@
         <v>250</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="21"/>
-      <c r="B75" s="21"/>
+    <row r="75" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="12"/>
+      <c r="B75" s="12"/>
       <c r="C75" s="2">
         <v>250</v>
       </c>
       <c r="D75" s="2">
         <v>400</v>
       </c>
-      <c r="E75" s="16">
+      <c r="E75" s="7">
         <v>900</v>
       </c>
       <c r="F75" s="2">
@@ -2709,16 +2710,16 @@
         <v>250</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="21"/>
-      <c r="B76" s="21"/>
+    <row r="76" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="12"/>
+      <c r="B76" s="12"/>
       <c r="C76" s="2">
         <v>250</v>
       </c>
       <c r="D76" s="2">
         <v>400</v>
       </c>
-      <c r="E76" s="16">
+      <c r="E76" s="7">
         <v>900</v>
       </c>
       <c r="F76" s="2">
@@ -2728,7 +2729,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
         <v>65</v>
       </c>
@@ -2741,7 +2742,7 @@
       <c r="D77" s="2">
         <v>400</v>
       </c>
-      <c r="E77" s="16">
+      <c r="E77" s="7">
         <v>900</v>
       </c>
       <c r="F77" s="2">
@@ -2751,7 +2752,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
         <v>66</v>
       </c>
@@ -2764,7 +2765,7 @@
       <c r="D78" s="2">
         <v>400</v>
       </c>
-      <c r="E78" s="16">
+      <c r="E78" s="7">
         <v>900</v>
       </c>
       <c r="F78" s="2">
@@ -2774,7 +2775,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
         <v>67</v>
       </c>
@@ -2787,7 +2788,7 @@
       <c r="D79" s="2">
         <v>400</v>
       </c>
-      <c r="E79" s="16">
+      <c r="E79" s="7">
         <v>900</v>
       </c>
       <c r="F79" s="2">
@@ -2797,7 +2798,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
         <v>68</v>
       </c>
@@ -2810,7 +2811,7 @@
       <c r="D80" s="2">
         <v>400</v>
       </c>
-      <c r="E80" s="16">
+      <c r="E80" s="7">
         <v>900</v>
       </c>
       <c r="F80" s="2">
@@ -2820,7 +2821,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
         <v>69</v>
       </c>
@@ -2833,7 +2834,7 @@
       <c r="D81" s="2">
         <v>400</v>
       </c>
-      <c r="E81" s="16">
+      <c r="E81" s="7">
         <v>900</v>
       </c>
       <c r="F81" s="2">
@@ -2843,7 +2844,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
         <v>70</v>
       </c>
@@ -2856,7 +2857,7 @@
       <c r="D82" s="2">
         <v>400</v>
       </c>
-      <c r="E82" s="16">
+      <c r="E82" s="7">
         <v>900</v>
       </c>
       <c r="F82" s="2">
@@ -2866,7 +2867,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
         <v>71</v>
       </c>
@@ -2879,7 +2880,7 @@
       <c r="D83" s="2">
         <v>400</v>
       </c>
-      <c r="E83" s="16">
+      <c r="E83" s="7">
         <v>900</v>
       </c>
       <c r="F83" s="2">
@@ -2889,7 +2890,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
         <v>72</v>
       </c>
@@ -2902,7 +2903,7 @@
       <c r="D84" s="2">
         <v>400</v>
       </c>
-      <c r="E84" s="16">
+      <c r="E84" s="7">
         <v>900</v>
       </c>
       <c r="F84" s="2">
@@ -2912,7 +2913,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
         <v>73</v>
       </c>
@@ -2925,7 +2926,7 @@
       <c r="D85" s="2">
         <v>400</v>
       </c>
-      <c r="E85" s="16">
+      <c r="E85" s="7">
         <v>900</v>
       </c>
       <c r="F85" s="2">
@@ -2935,7 +2936,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
         <v>74</v>
       </c>
@@ -2948,7 +2949,7 @@
       <c r="D86" s="2">
         <v>400</v>
       </c>
-      <c r="E86" s="16">
+      <c r="E86" s="7">
         <v>900</v>
       </c>
       <c r="F86" s="2">
@@ -2958,7 +2959,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
         <v>75</v>
       </c>
@@ -2971,7 +2972,7 @@
       <c r="D87" s="2">
         <v>400</v>
       </c>
-      <c r="E87" s="16">
+      <c r="E87" s="7">
         <v>900</v>
       </c>
       <c r="F87" s="2">
@@ -2981,1318 +2982,2048 @@
         <v>250</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
       <c r="B88" s="5"/>
-      <c r="C88" s="17"/>
-      <c r="D88" s="17"/>
-      <c r="E88" s="17"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="8"/>
+      <c r="E88" s="8"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
     </row>
-    <row r="89" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="15" t="s">
+    <row r="89" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="B89" s="22"/>
-      <c r="C89" s="22"/>
-      <c r="D89" s="22"/>
-      <c r="E89" s="22"/>
-      <c r="F89" s="22"/>
-      <c r="G89" s="23"/>
-    </row>
-    <row r="90" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="9"/>
-      <c r="B90" s="10"/>
-      <c r="C90" s="10"/>
-      <c r="D90" s="10"/>
-      <c r="E90" s="10"/>
+      <c r="B89" s="17"/>
+      <c r="C89" s="17"/>
+      <c r="D89" s="17"/>
+      <c r="E89" s="17"/>
+      <c r="F89" s="17"/>
+      <c r="G89" s="18"/>
+    </row>
+    <row r="90" spans="1:7" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="21"/>
+      <c r="B90" s="22"/>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="4">
         <v>1</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="16"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C91" s="2">
+        <v>800</v>
+      </c>
+      <c r="D91" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E91" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F91" s="2">
+        <v>650</v>
+      </c>
+      <c r="G91" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
         <v>2</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="16"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C92" s="2">
+        <v>800</v>
+      </c>
+      <c r="D92" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E92" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F92" s="2">
+        <v>650</v>
+      </c>
+      <c r="G92" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
         <v>3</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="16"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C93" s="2">
+        <v>800</v>
+      </c>
+      <c r="D93" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E93" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F93" s="2">
+        <v>650</v>
+      </c>
+      <c r="G93" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
         <v>4</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="16"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C94" s="2">
+        <v>800</v>
+      </c>
+      <c r="D94" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E94" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F94" s="2">
+        <v>650</v>
+      </c>
+      <c r="G94" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
         <v>5</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="16"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C95" s="2">
+        <v>800</v>
+      </c>
+      <c r="D95" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E95" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F95" s="2">
+        <v>650</v>
+      </c>
+      <c r="G95" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="4">
         <v>6</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="16"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C96" s="2">
+        <v>800</v>
+      </c>
+      <c r="D96" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E96" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F96" s="2">
+        <v>650</v>
+      </c>
+      <c r="G96" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="4">
         <v>7</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="16"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C97" s="2">
+        <v>800</v>
+      </c>
+      <c r="D97" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E97" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F97" s="2">
+        <v>650</v>
+      </c>
+      <c r="G97" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="4">
         <v>8</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="16"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C98" s="2">
+        <v>800</v>
+      </c>
+      <c r="D98" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E98" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F98" s="2">
+        <v>650</v>
+      </c>
+      <c r="G98" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="4">
         <v>9</v>
       </c>
-      <c r="B99" s="20" t="s">
+      <c r="B99" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="16"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C99" s="2">
+        <v>800</v>
+      </c>
+      <c r="D99" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E99" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F99" s="2">
+        <v>650</v>
+      </c>
+      <c r="G99" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="4">
         <v>10</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="16"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C100" s="2">
+        <v>800</v>
+      </c>
+      <c r="D100" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E100" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F100" s="2">
+        <v>650</v>
+      </c>
+      <c r="G100" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
         <v>11</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="16"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C101" s="2">
+        <v>800</v>
+      </c>
+      <c r="D101" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E101" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F101" s="2">
+        <v>650</v>
+      </c>
+      <c r="G101" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="4">
         <v>12</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="16"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C102" s="2">
+        <v>800</v>
+      </c>
+      <c r="D102" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E102" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F102" s="2">
+        <v>650</v>
+      </c>
+      <c r="G102" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="4">
         <v>13</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="16"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C103" s="2">
+        <v>800</v>
+      </c>
+      <c r="D103" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E103" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F103" s="2">
+        <v>650</v>
+      </c>
+      <c r="G103" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="4">
         <v>14</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="16"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C104" s="2">
+        <v>800</v>
+      </c>
+      <c r="D104" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E104" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F104" s="2">
+        <v>650</v>
+      </c>
+      <c r="G104" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="4">
         <v>15</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="16"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C105" s="2">
+        <v>800</v>
+      </c>
+      <c r="D105" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E105" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F105" s="2">
+        <v>650</v>
+      </c>
+      <c r="G105" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="4">
         <v>16</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="16"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C106" s="2">
+        <v>800</v>
+      </c>
+      <c r="D106" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E106" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F106" s="2">
+        <v>650</v>
+      </c>
+      <c r="G106" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="4">
         <v>17</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="16"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C107" s="2">
+        <v>800</v>
+      </c>
+      <c r="D107" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E107" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F107" s="2">
+        <v>650</v>
+      </c>
+      <c r="G107" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="4">
         <v>18</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="16"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C108" s="2">
+        <v>800</v>
+      </c>
+      <c r="D108" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E108" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F108" s="2">
+        <v>650</v>
+      </c>
+      <c r="G108" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="4">
         <v>19</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="16"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C109" s="2">
+        <v>800</v>
+      </c>
+      <c r="D109" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E109" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F109" s="2">
+        <v>650</v>
+      </c>
+      <c r="G109" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="4">
         <v>20</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
-      <c r="E110" s="16"/>
-      <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C110" s="2">
+        <v>800</v>
+      </c>
+      <c r="D110" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E110" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F110" s="2">
+        <v>650</v>
+      </c>
+      <c r="G110" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="4">
         <v>21</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
-      <c r="E111" s="16"/>
-      <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C111" s="2">
+        <v>800</v>
+      </c>
+      <c r="D111" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E111" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F111" s="2">
+        <v>650</v>
+      </c>
+      <c r="G111" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
         <v>22</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
-      <c r="E112" s="16"/>
-      <c r="F112" s="2"/>
-      <c r="G112" s="2"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C112" s="2">
+        <v>800</v>
+      </c>
+      <c r="D112" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E112" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F112" s="2">
+        <v>650</v>
+      </c>
+      <c r="G112" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="4">
         <v>23</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
-      <c r="E113" s="16"/>
-      <c r="F113" s="2"/>
-      <c r="G113" s="2"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C113" s="2">
+        <v>800</v>
+      </c>
+      <c r="D113" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E113" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F113" s="2">
+        <v>650</v>
+      </c>
+      <c r="G113" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="4">
         <v>24</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
-      <c r="E114" s="16"/>
-      <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C114" s="2">
+        <v>800</v>
+      </c>
+      <c r="D114" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E114" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F114" s="2">
+        <v>650</v>
+      </c>
+      <c r="G114" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="4">
         <v>25</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
-      <c r="E115" s="16"/>
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C115" s="2">
+        <v>800</v>
+      </c>
+      <c r="D115" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E115" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F115" s="2">
+        <v>650</v>
+      </c>
+      <c r="G115" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="4">
         <v>26</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="16"/>
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C116" s="2">
+        <v>800</v>
+      </c>
+      <c r="D116" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E116" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F116" s="2">
+        <v>650</v>
+      </c>
+      <c r="G116" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="4">
         <v>27</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
-      <c r="E117" s="16"/>
-      <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C117" s="2">
+        <v>800</v>
+      </c>
+      <c r="D117" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E117" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F117" s="2">
+        <v>650</v>
+      </c>
+      <c r="G117" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="4">
         <v>28</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
-      <c r="E118" s="16"/>
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C118" s="2">
+        <v>800</v>
+      </c>
+      <c r="D118" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E118" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F118" s="2">
+        <v>650</v>
+      </c>
+      <c r="G118" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="4">
         <v>29</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
-      <c r="E119" s="16"/>
-      <c r="F119" s="2"/>
-      <c r="G119" s="2"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C119" s="2">
+        <v>800</v>
+      </c>
+      <c r="D119" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E119" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F119" s="2">
+        <v>650</v>
+      </c>
+      <c r="G119" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="4">
         <v>30</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C120" s="2"/>
-      <c r="D120" s="2"/>
-      <c r="E120" s="16"/>
-      <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C120" s="2">
+        <v>800</v>
+      </c>
+      <c r="D120" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E120" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F120" s="2">
+        <v>650</v>
+      </c>
+      <c r="G120" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="4">
         <v>31</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
-      <c r="E121" s="16"/>
-      <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C121" s="2">
+        <v>800</v>
+      </c>
+      <c r="D121" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E121" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F121" s="2">
+        <v>650</v>
+      </c>
+      <c r="G121" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="4">
         <v>32</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C122" s="2"/>
-      <c r="D122" s="2"/>
-      <c r="E122" s="16"/>
-      <c r="F122" s="2"/>
-      <c r="G122" s="2"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C122" s="2">
+        <v>800</v>
+      </c>
+      <c r="D122" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E122" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F122" s="2">
+        <v>650</v>
+      </c>
+      <c r="G122" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
         <v>33</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C123" s="2"/>
-      <c r="D123" s="2"/>
-      <c r="E123" s="16"/>
-      <c r="F123" s="2"/>
-      <c r="G123" s="2"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C123" s="2">
+        <v>800</v>
+      </c>
+      <c r="D123" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E123" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F123" s="2">
+        <v>650</v>
+      </c>
+      <c r="G123" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="4">
         <v>34</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C124" s="2"/>
-      <c r="D124" s="2"/>
-      <c r="E124" s="16"/>
-      <c r="F124" s="2"/>
-      <c r="G124" s="2"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C124" s="2">
+        <v>800</v>
+      </c>
+      <c r="D124" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E124" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F124" s="2">
+        <v>650</v>
+      </c>
+      <c r="G124" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="4">
         <v>35</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C125" s="2"/>
-      <c r="D125" s="2"/>
-      <c r="E125" s="16"/>
-      <c r="F125" s="2"/>
-      <c r="G125" s="2"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C125" s="2">
+        <v>800</v>
+      </c>
+      <c r="D125" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E125" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F125" s="2">
+        <v>650</v>
+      </c>
+      <c r="G125" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="4"/>
       <c r="B126" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C126" s="2"/>
-      <c r="D126" s="2"/>
-      <c r="E126" s="16"/>
-      <c r="F126" s="2"/>
-      <c r="G126" s="2"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C126" s="2">
+        <v>800</v>
+      </c>
+      <c r="D126" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E126" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F126" s="2">
+        <v>650</v>
+      </c>
+      <c r="G126" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="4"/>
       <c r="B127" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C127" s="2"/>
-      <c r="D127" s="2"/>
-      <c r="E127" s="16"/>
-      <c r="F127" s="2"/>
-      <c r="G127" s="2"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C127" s="2">
+        <v>800</v>
+      </c>
+      <c r="D127" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E127" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F127" s="2">
+        <v>650</v>
+      </c>
+      <c r="G127" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="4"/>
       <c r="B128" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C128" s="2"/>
-      <c r="D128" s="2"/>
-      <c r="E128" s="16"/>
-      <c r="F128" s="2"/>
-      <c r="G128" s="2"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C128" s="2">
+        <v>800</v>
+      </c>
+      <c r="D128" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E128" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F128" s="2">
+        <v>650</v>
+      </c>
+      <c r="G128" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="4"/>
       <c r="B129" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
-      <c r="E129" s="16"/>
-      <c r="F129" s="2"/>
-      <c r="G129" s="2"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C129" s="2">
+        <v>800</v>
+      </c>
+      <c r="D129" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E129" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F129" s="2">
+        <v>650</v>
+      </c>
+      <c r="G129" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="4"/>
       <c r="B130" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C130" s="2"/>
-      <c r="D130" s="2"/>
-      <c r="E130" s="16"/>
-      <c r="F130" s="2"/>
-      <c r="G130" s="2"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C130" s="2">
+        <v>800</v>
+      </c>
+      <c r="D130" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E130" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F130" s="2">
+        <v>650</v>
+      </c>
+      <c r="G130" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="4"/>
       <c r="B131" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
-      <c r="E131" s="16"/>
-      <c r="F131" s="2"/>
-      <c r="G131" s="2"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C131" s="2">
+        <v>800</v>
+      </c>
+      <c r="D131" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E131" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F131" s="2">
+        <v>650</v>
+      </c>
+      <c r="G131" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="4"/>
       <c r="B132" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
-      <c r="E132" s="16"/>
-      <c r="F132" s="2"/>
-      <c r="G132" s="2"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C132" s="2">
+        <v>800</v>
+      </c>
+      <c r="D132" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E132" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F132" s="2">
+        <v>650</v>
+      </c>
+      <c r="G132" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="4"/>
       <c r="B133" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
-      <c r="E133" s="16"/>
-      <c r="F133" s="2"/>
-      <c r="G133" s="2"/>
-    </row>
-    <row r="134" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A134" s="7" t="s">
+      <c r="C133" s="2">
+        <v>800</v>
+      </c>
+      <c r="D133" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E133" s="7">
+        <v>1600</v>
+      </c>
+      <c r="F133" s="2">
+        <v>650</v>
+      </c>
+      <c r="G133" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="23.25" x14ac:dyDescent="0.2">
+      <c r="A134" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B134" s="8"/>
-      <c r="C134" s="8"/>
-      <c r="D134" s="8"/>
-      <c r="E134" s="8"/>
+      <c r="B134" s="20"/>
+      <c r="C134" s="20"/>
+      <c r="D134" s="20"/>
+      <c r="E134" s="20"/>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="4">
         <v>1</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C135" s="2"/>
-      <c r="D135" s="2"/>
-      <c r="E135" s="16"/>
-      <c r="F135" s="2"/>
-      <c r="G135" s="2"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C135" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D135" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E135" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F135" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G135" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="4">
         <v>2</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C136" s="2"/>
-      <c r="D136" s="2"/>
-      <c r="E136" s="16"/>
-      <c r="F136" s="2"/>
-      <c r="G136" s="2"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C136" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D136" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E136" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F136" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G136" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="4">
         <v>3</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C137" s="2"/>
-      <c r="D137" s="2"/>
-      <c r="E137" s="16"/>
-      <c r="F137" s="2"/>
-      <c r="G137" s="2"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C137" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D137" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E137" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F137" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G137" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="4">
         <v>4</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C138" s="2"/>
-      <c r="D138" s="2"/>
-      <c r="E138" s="16"/>
-      <c r="F138" s="2"/>
-      <c r="G138" s="2"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C138" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D138" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E138" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F138" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G138" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="4">
         <v>5</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C139" s="2"/>
-      <c r="D139" s="2"/>
-      <c r="E139" s="16"/>
-      <c r="F139" s="2"/>
-      <c r="G139" s="2"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C139" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D139" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E139" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F139" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G139" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="4">
         <v>6</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C140" s="2"/>
-      <c r="D140" s="2"/>
-      <c r="E140" s="16"/>
-      <c r="F140" s="2"/>
-      <c r="G140" s="2"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C140" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D140" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E140" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F140" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G140" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="4">
         <v>7</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C141" s="2"/>
-      <c r="D141" s="2"/>
-      <c r="E141" s="16"/>
-      <c r="F141" s="2"/>
-      <c r="G141" s="2"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C141" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D141" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E141" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F141" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G141" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="4">
         <v>8</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
-      <c r="E142" s="16"/>
-      <c r="F142" s="2"/>
-      <c r="G142" s="2"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C142" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D142" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E142" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F142" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G142" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="4">
         <v>9</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C143" s="2"/>
-      <c r="D143" s="2"/>
-      <c r="E143" s="16"/>
-      <c r="F143" s="2"/>
-      <c r="G143" s="2"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C143" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D143" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E143" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F143" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G143" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="4">
         <v>10</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C144" s="2"/>
-      <c r="D144" s="2"/>
-      <c r="E144" s="16"/>
-      <c r="F144" s="2"/>
-      <c r="G144" s="2"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C144" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D144" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E144" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F144" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G144" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
         <v>11</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
-      <c r="E145" s="16"/>
-      <c r="F145" s="2"/>
-      <c r="G145" s="2"/>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C145" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D145" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E145" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F145" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G145" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="4">
         <v>12</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
-      <c r="E146" s="16"/>
-      <c r="F146" s="2"/>
-      <c r="G146" s="2"/>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C146" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D146" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E146" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F146" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G146" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="4">
         <v>13</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
-      <c r="E147" s="16"/>
-      <c r="F147" s="2"/>
-      <c r="G147" s="2"/>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C147" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D147" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E147" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F147" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G147" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="4">
         <v>14</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C148" s="2"/>
-      <c r="D148" s="2"/>
-      <c r="E148" s="16"/>
-      <c r="F148" s="2"/>
-      <c r="G148" s="2"/>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C148" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D148" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E148" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F148" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G148" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="4">
         <v>15</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C149" s="2"/>
-      <c r="D149" s="2"/>
-      <c r="E149" s="16"/>
-      <c r="F149" s="2"/>
-      <c r="G149" s="2"/>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C149" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D149" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E149" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F149" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G149" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="4"/>
       <c r="B150" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C150" s="2"/>
-      <c r="D150" s="2"/>
-      <c r="E150" s="16"/>
-      <c r="F150" s="2"/>
-      <c r="G150" s="2"/>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C150" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D150" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E150" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F150" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G150" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="4"/>
       <c r="B151" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C151" s="2"/>
-      <c r="D151" s="2"/>
-      <c r="E151" s="16"/>
-      <c r="F151" s="2"/>
-      <c r="G151" s="2"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C151" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D151" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E151" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F151" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G151" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="4"/>
       <c r="B152" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C152" s="2"/>
-      <c r="D152" s="2"/>
-      <c r="E152" s="16"/>
-      <c r="F152" s="2"/>
-      <c r="G152" s="2"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C152" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D152" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E152" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F152" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G152" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="4"/>
       <c r="B153" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C153" s="2"/>
-      <c r="D153" s="2"/>
-      <c r="E153" s="16"/>
-      <c r="F153" s="2"/>
-      <c r="G153" s="2"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C153" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D153" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E153" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F153" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G153" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="4"/>
       <c r="B154" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C154" s="2"/>
-      <c r="D154" s="2"/>
-      <c r="E154" s="16"/>
-      <c r="F154" s="2"/>
-      <c r="G154" s="2"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C154" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D154" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E154" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F154" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G154" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="4"/>
       <c r="B155" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C155" s="2"/>
-      <c r="D155" s="2"/>
-      <c r="E155" s="16"/>
-      <c r="F155" s="2"/>
-      <c r="G155" s="2"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C155" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D155" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E155" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F155" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G155" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" s="4"/>
       <c r="B156" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C156" s="2"/>
-      <c r="D156" s="2"/>
-      <c r="E156" s="16"/>
-      <c r="F156" s="2"/>
-      <c r="G156" s="2"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C156" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D156" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E156" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F156" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G156" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" s="4"/>
       <c r="B157" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C157" s="2"/>
-      <c r="D157" s="2"/>
-      <c r="E157" s="16"/>
-      <c r="F157" s="2"/>
-      <c r="G157" s="2"/>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C157" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D157" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E157" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F157" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G157" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" s="4"/>
       <c r="B158" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C158" s="2"/>
-      <c r="D158" s="2"/>
-      <c r="E158" s="16"/>
-      <c r="F158" s="2"/>
-      <c r="G158" s="2"/>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C158" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D158" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E158" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F158" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G158" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" s="4"/>
       <c r="B159" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C159" s="2"/>
-      <c r="D159" s="2"/>
-      <c r="E159" s="16"/>
-      <c r="F159" s="2"/>
-      <c r="G159" s="2"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C159" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D159" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E159" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F159" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G159" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" s="4"/>
       <c r="B160" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C160" s="2"/>
-      <c r="D160" s="2"/>
-      <c r="E160" s="16"/>
-      <c r="F160" s="2"/>
-      <c r="G160" s="2"/>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C160" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D160" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E160" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F160" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G160" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" s="4"/>
       <c r="B161" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C161" s="2"/>
-      <c r="D161" s="2"/>
-      <c r="E161" s="16"/>
-      <c r="F161" s="2"/>
-      <c r="G161" s="2"/>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C161" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D161" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E161" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F161" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G161" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" s="4"/>
       <c r="B162" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C162" s="2"/>
-      <c r="D162" s="2"/>
-      <c r="E162" s="16"/>
-      <c r="F162" s="2"/>
-      <c r="G162" s="2"/>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C162" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D162" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E162" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F162" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G162" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" s="4"/>
       <c r="B163" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C163" s="2"/>
-      <c r="D163" s="2"/>
-      <c r="E163" s="16"/>
-      <c r="F163" s="2"/>
-      <c r="G163" s="2"/>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C163" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D163" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E163" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F163" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G163" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" s="4"/>
       <c r="B164" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C164" s="2"/>
-      <c r="D164" s="2"/>
-      <c r="E164" s="16"/>
-      <c r="F164" s="2"/>
-      <c r="G164" s="2"/>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C164" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D164" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E164" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F164" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G164" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
-      <c r="E165" s="16"/>
+      <c r="E165" s="7"/>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
-      <c r="E166" s="16"/>
+      <c r="E166" s="7"/>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
-      <c r="E167" s="16"/>
+      <c r="E167" s="7"/>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
-      <c r="E168" s="16"/>
+      <c r="E168" s="7"/>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="2"/>
       <c r="D169" s="2"/>
-      <c r="E169" s="16"/>
+      <c r="E169" s="7"/>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
-      <c r="E170" s="16"/>
+      <c r="E170" s="7"/>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
-      <c r="E171" s="16"/>
+      <c r="E171" s="7"/>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
-      <c r="E172" s="16"/>
+      <c r="E172" s="7"/>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
-      <c r="E173" s="16"/>
+      <c r="E173" s="7"/>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
-      <c r="E174" s="16"/>
+      <c r="E174" s="7"/>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
-      <c r="E175" s="16"/>
+      <c r="E175" s="7"/>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
-      <c r="E176" s="16"/>
+      <c r="E176" s="7"/>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
-      <c r="E177" s="16"/>
+      <c r="E177" s="7"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
-      <c r="E178" s="16"/>
+      <c r="E178" s="7"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
-      <c r="E179" s="16"/>
+      <c r="E179" s="7"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
-      <c r="E180" s="16"/>
+      <c r="E180" s="7"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
-      <c r="E181" s="16"/>
+      <c r="E181" s="7"/>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
-      <c r="E182" s="16"/>
+      <c r="E182" s="7"/>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="2"/>
       <c r="D183" s="2"/>
-      <c r="E183" s="16"/>
+      <c r="E183" s="7"/>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
-      <c r="E184" s="16"/>
+      <c r="E184" s="7"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
-      <c r="E185" s="16"/>
+      <c r="E185" s="7"/>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
-      <c r="E186" s="16"/>
+      <c r="E186" s="7"/>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
-      <c r="E187" s="16"/>
+      <c r="E187" s="7"/>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
-      <c r="E188" s="16"/>
+      <c r="E188" s="7"/>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
-      <c r="E189" s="16"/>
+      <c r="E189" s="7"/>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
-      <c r="E190" s="16"/>
+      <c r="E190" s="7"/>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
-      <c r="E191" s="16"/>
+      <c r="E191" s="7"/>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
-      <c r="E192" s="16"/>
+      <c r="E192" s="7"/>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
-      <c r="E193" s="16"/>
+      <c r="E193" s="7"/>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
-      <c r="E194" s="16"/>
+      <c r="E194" s="7"/>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
-      <c r="E195" s="16"/>
+      <c r="E195" s="7"/>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
-      <c r="E196" s="16"/>
+      <c r="E196" s="7"/>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
-      <c r="E197" s="16"/>
+      <c r="E197" s="7"/>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
-      <c r="E198" s="16"/>
+      <c r="E198" s="7"/>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
-      <c r="E199" s="16"/>
+      <c r="E199" s="7"/>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
-      <c r="E200" s="16"/>
+      <c r="E200" s="7"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
-      <c r="E201" s="16"/>
+      <c r="E201" s="7"/>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
-      <c r="E202" s="16"/>
+      <c r="E202" s="7"/>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
-      <c r="E203" s="16"/>
+      <c r="E203" s="7"/>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
-      <c r="E204" s="16"/>
+      <c r="E204" s="7"/>
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A205" s="18"/>
-      <c r="B205" s="18"/>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A205" s="9"/>
+      <c r="B205" s="9"/>
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="2"/>
@@ -4300,7 +5031,7 @@
       <c r="F206" s="2"/>
       <c r="G206" s="2"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="2"/>
@@ -4308,7 +5039,7 @@
       <c r="F207" s="2"/>
       <c r="G207" s="2"/>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A208" s="4"/>
       <c r="B208" s="4"/>
       <c r="C208" s="2"/>
@@ -4316,7 +5047,7 @@
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="2"/>
@@ -4324,7 +5055,7 @@
       <c r="F209" s="2"/>
       <c r="G209" s="2"/>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="2"/>
@@ -4332,7 +5063,7 @@
       <c r="F210" s="2"/>
       <c r="G210" s="2"/>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="2"/>
@@ -4340,7 +5071,7 @@
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="2"/>
@@ -4348,7 +5079,7 @@
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="2"/>
@@ -4356,7 +5087,7 @@
       <c r="F213" s="2"/>
       <c r="G213" s="2"/>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="2"/>
@@ -4364,7 +5095,7 @@
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A215" s="4"/>
       <c r="B215" s="4"/>
       <c r="C215" s="2"/>
@@ -4372,7 +5103,7 @@
       <c r="F215" s="2"/>
       <c r="G215" s="2"/>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="2"/>
@@ -4380,7 +5111,7 @@
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="2"/>
@@ -4388,7 +5119,7 @@
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
       <c r="C218" s="2"/>
@@ -4396,7 +5127,7 @@
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="2"/>
@@ -4404,7 +5135,7 @@
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="2"/>
@@ -4412,7 +5143,7 @@
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" s="4"/>
       <c r="B221" s="4"/>
       <c r="C221" s="2"/>
@@ -4420,7 +5151,7 @@
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222" s="4"/>
       <c r="B222" s="4"/>
       <c r="C222" s="2"/>
@@ -4428,7 +5159,7 @@
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223" s="4"/>
       <c r="B223" s="4"/>
       <c r="C223" s="2"/>
@@ -4436,7 +5167,7 @@
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224" s="4"/>
       <c r="B224" s="4"/>
       <c r="C224" s="2"/>
@@ -4444,7 +5175,7 @@
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225" s="4"/>
       <c r="B225" s="4"/>
       <c r="C225" s="2"/>
@@ -4452,7 +5183,7 @@
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A226" s="4"/>
       <c r="B226" s="4"/>
       <c r="C226" s="2"/>
@@ -4460,7 +5191,7 @@
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227" s="4"/>
       <c r="B227" s="4"/>
       <c r="C227" s="2"/>
@@ -4468,7 +5199,7 @@
       <c r="F227" s="2"/>
       <c r="G227" s="2"/>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="2"/>
@@ -4476,7 +5207,7 @@
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="2"/>
@@ -4484,7 +5215,7 @@
       <c r="F229" s="2"/>
       <c r="G229" s="2"/>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="2"/>
@@ -4492,7 +5223,7 @@
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="2"/>
@@ -4500,7 +5231,7 @@
       <c r="F231" s="2"/>
       <c r="G231" s="2"/>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="2"/>
@@ -4508,7 +5239,7 @@
       <c r="F232" s="2"/>
       <c r="G232" s="2"/>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="2"/>
@@ -4516,7 +5247,7 @@
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234" s="4"/>
       <c r="B234" s="4"/>
       <c r="C234" s="2"/>
@@ -4524,7 +5255,7 @@
       <c r="F234" s="2"/>
       <c r="G234" s="2"/>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="2"/>
@@ -4532,7 +5263,7 @@
       <c r="F235" s="2"/>
       <c r="G235" s="2"/>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="2"/>
@@ -4540,7 +5271,7 @@
       <c r="F236" s="2"/>
       <c r="G236" s="2"/>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="2"/>
@@ -4548,7 +5279,7 @@
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="2"/>
@@ -4556,7 +5287,7 @@
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="2"/>
@@ -4564,7 +5295,7 @@
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="2"/>
@@ -4572,7 +5303,7 @@
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241" s="4"/>
       <c r="B241" s="4"/>
       <c r="C241" s="2"/>
@@ -4580,7 +5311,7 @@
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A242" s="4"/>
       <c r="B242" s="4"/>
       <c r="C242" s="2"/>
@@ -4588,7 +5319,7 @@
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A243" s="4"/>
       <c r="B243" s="4"/>
       <c r="C243" s="2"/>
@@ -4596,7 +5327,7 @@
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A244" s="4"/>
       <c r="B244" s="4"/>
       <c r="C244" s="2"/>
@@ -4604,7 +5335,7 @@
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A245" s="4"/>
       <c r="B245" s="4"/>
       <c r="C245" s="2"/>
@@ -4612,7 +5343,7 @@
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A246" s="4"/>
       <c r="B246" s="4"/>
       <c r="C246" s="2"/>
@@ -4620,7 +5351,7 @@
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="2"/>
@@ -4628,7 +5359,7 @@
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="2"/>
@@ -4636,7 +5367,7 @@
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="2"/>
@@ -4644,7 +5375,7 @@
       <c r="F249" s="2"/>
       <c r="G249" s="2"/>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="2"/>
@@ -4652,7 +5383,7 @@
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A251" s="4"/>
       <c r="B251" s="4"/>
       <c r="C251" s="2"/>
@@ -4660,7 +5391,7 @@
       <c r="F251" s="2"/>
       <c r="G251" s="2"/>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A252" s="4"/>
       <c r="B252" s="4"/>
       <c r="C252" s="2"/>
@@ -4668,7 +5399,7 @@
       <c r="F252" s="2"/>
       <c r="G252" s="2"/>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A253" s="4"/>
       <c r="B253" s="4"/>
       <c r="C253" s="2"/>
@@ -4676,7 +5407,7 @@
       <c r="F253" s="2"/>
       <c r="G253" s="2"/>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A254" s="4"/>
       <c r="B254" s="4"/>
       <c r="C254" s="2"/>
@@ -4684,7 +5415,7 @@
       <c r="F254" s="2"/>
       <c r="G254" s="2"/>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A255" s="4"/>
       <c r="B255" s="4"/>
       <c r="C255" s="2"/>
@@ -4692,7 +5423,7 @@
       <c r="F255" s="2"/>
       <c r="G255" s="2"/>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A256" s="4"/>
       <c r="B256" s="4"/>
       <c r="C256" s="2"/>
@@ -4700,7 +5431,7 @@
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" s="4"/>
       <c r="B257" s="4"/>
       <c r="C257" s="2"/>
@@ -4708,7 +5439,7 @@
       <c r="F257" s="2"/>
       <c r="G257" s="2"/>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" s="4"/>
       <c r="B258" s="4"/>
       <c r="C258" s="2"/>
@@ -4716,7 +5447,7 @@
       <c r="F258" s="2"/>
       <c r="G258" s="2"/>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" s="4"/>
       <c r="B259" s="4"/>
       <c r="C259" s="2"/>
@@ -4724,7 +5455,7 @@
       <c r="F259" s="2"/>
       <c r="G259" s="2"/>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" s="4"/>
       <c r="B260" s="4"/>
       <c r="C260" s="2"/>
@@ -4732,7 +5463,7 @@
       <c r="F260" s="2"/>
       <c r="G260" s="2"/>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" s="4"/>
       <c r="B261" s="4"/>
       <c r="C261" s="2"/>
@@ -4740,7 +5471,7 @@
       <c r="F261" s="2"/>
       <c r="G261" s="2"/>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" s="4"/>
       <c r="B262" s="4"/>
       <c r="C262" s="2"/>
@@ -4748,7 +5479,7 @@
       <c r="F262" s="2"/>
       <c r="G262" s="2"/>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" s="4"/>
       <c r="B263" s="4"/>
       <c r="C263" s="2"/>
@@ -4756,7 +5487,7 @@
       <c r="F263" s="2"/>
       <c r="G263" s="2"/>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" s="4"/>
       <c r="B264" s="4"/>
       <c r="C264" s="2"/>
@@ -4764,7 +5495,7 @@
       <c r="F264" s="2"/>
       <c r="G264" s="2"/>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265" s="4"/>
       <c r="B265" s="4"/>
       <c r="C265" s="2"/>
@@ -4772,7 +5503,7 @@
       <c r="F265" s="2"/>
       <c r="G265" s="2"/>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" s="4"/>
       <c r="B266" s="4"/>
       <c r="C266" s="2"/>
@@ -4780,7 +5511,7 @@
       <c r="F266" s="2"/>
       <c r="G266" s="2"/>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="2"/>
@@ -4788,7 +5519,7 @@
       <c r="F267" s="2"/>
       <c r="G267" s="2"/>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="2"/>
@@ -4796,7 +5527,7 @@
       <c r="F268" s="2"/>
       <c r="G268" s="2"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="2"/>
@@ -4804,7 +5535,7 @@
       <c r="F269" s="2"/>
       <c r="G269" s="2"/>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="2"/>
@@ -4812,7 +5543,7 @@
       <c r="F270" s="2"/>
       <c r="G270" s="2"/>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="2"/>
@@ -4820,7 +5551,7 @@
       <c r="F271" s="2"/>
       <c r="G271" s="2"/>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="2"/>
@@ -4828,7 +5559,7 @@
       <c r="F272" s="2"/>
       <c r="G272" s="2"/>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273" s="4"/>
       <c r="B273" s="4"/>
       <c r="C273" s="2"/>
@@ -4836,7 +5567,7 @@
       <c r="F273" s="2"/>
       <c r="G273" s="2"/>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="2"/>
@@ -4844,7 +5575,7 @@
       <c r="F274" s="2"/>
       <c r="G274" s="2"/>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="2"/>
@@ -4852,7 +5583,7 @@
       <c r="F275" s="2"/>
       <c r="G275" s="2"/>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="2"/>
@@ -4860,7 +5591,7 @@
       <c r="F276" s="2"/>
       <c r="G276" s="2"/>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="2"/>
@@ -4868,7 +5599,7 @@
       <c r="F277" s="2"/>
       <c r="G277" s="2"/>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="2"/>
@@ -4876,7 +5607,7 @@
       <c r="F278" s="2"/>
       <c r="G278" s="2"/>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="2"/>
@@ -4884,7 +5615,7 @@
       <c r="F279" s="2"/>
       <c r="G279" s="2"/>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A280" s="4"/>
       <c r="B280" s="4"/>
       <c r="C280" s="2"/>
@@ -4892,7 +5623,7 @@
       <c r="F280" s="2"/>
       <c r="G280" s="2"/>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A281" s="4"/>
       <c r="B281" s="4"/>
       <c r="C281" s="2"/>
@@ -4900,7 +5631,7 @@
       <c r="F281" s="2"/>
       <c r="G281" s="2"/>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282" s="4"/>
       <c r="B282" s="4"/>
       <c r="C282" s="2"/>
@@ -4908,7 +5639,7 @@
       <c r="F282" s="2"/>
       <c r="G282" s="2"/>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A283" s="4"/>
       <c r="B283" s="4"/>
       <c r="C283" s="2"/>
@@ -4916,7 +5647,7 @@
       <c r="F283" s="2"/>
       <c r="G283" s="2"/>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A284" s="4"/>
       <c r="B284" s="4"/>
       <c r="C284" s="2"/>
@@ -4924,7 +5655,7 @@
       <c r="F284" s="2"/>
       <c r="G284" s="2"/>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A285" s="4"/>
       <c r="B285" s="4"/>
       <c r="C285" s="2"/>
@@ -4932,7 +5663,7 @@
       <c r="F285" s="2"/>
       <c r="G285" s="2"/>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="2"/>
@@ -4940,7 +5671,7 @@
       <c r="F286" s="2"/>
       <c r="G286" s="2"/>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="2"/>
@@ -4948,7 +5679,7 @@
       <c r="F287" s="2"/>
       <c r="G287" s="2"/>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="2"/>
@@ -4956,7 +5687,7 @@
       <c r="F288" s="2"/>
       <c r="G288" s="2"/>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
       <c r="C289" s="2"/>
@@ -4964,7 +5695,7 @@
       <c r="F289" s="2"/>
       <c r="G289" s="2"/>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A290" s="4"/>
       <c r="B290" s="4"/>
       <c r="C290" s="2"/>
@@ -4972,7 +5703,7 @@
       <c r="F290" s="2"/>
       <c r="G290" s="2"/>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A291" s="4"/>
       <c r="B291" s="4"/>
       <c r="C291" s="2"/>
@@ -4980,7 +5711,7 @@
       <c r="F291" s="2"/>
       <c r="G291" s="2"/>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A292" s="4"/>
       <c r="B292" s="4"/>
       <c r="C292" s="2"/>
@@ -4988,7 +5719,7 @@
       <c r="F292" s="2"/>
       <c r="G292" s="2"/>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A293" s="4"/>
       <c r="B293" s="4"/>
       <c r="C293" s="2"/>
@@ -4996,7 +5727,7 @@
       <c r="F293" s="2"/>
       <c r="G293" s="2"/>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A294" s="4"/>
       <c r="B294" s="4"/>
       <c r="C294" s="2"/>
@@ -5004,7 +5735,7 @@
       <c r="F294" s="2"/>
       <c r="G294" s="2"/>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A295" s="4"/>
       <c r="B295" s="4"/>
       <c r="C295" s="2"/>
@@ -5012,7 +5743,7 @@
       <c r="F295" s="2"/>
       <c r="G295" s="2"/>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A296" s="4"/>
       <c r="B296" s="4"/>
       <c r="C296" s="2"/>
@@ -5020,7 +5751,7 @@
       <c r="F296" s="2"/>
       <c r="G296" s="2"/>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A297" s="4"/>
       <c r="B297" s="4"/>
       <c r="C297" s="2"/>
@@ -5028,7 +5759,7 @@
       <c r="F297" s="2"/>
       <c r="G297" s="2"/>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A298" s="4"/>
       <c r="B298" s="4"/>
       <c r="C298" s="2"/>
@@ -5036,7 +5767,7 @@
       <c r="F298" s="2"/>
       <c r="G298" s="2"/>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A299" s="4"/>
       <c r="B299" s="4"/>
       <c r="C299" s="2"/>
@@ -5044,7 +5775,7 @@
       <c r="F299" s="2"/>
       <c r="G299" s="2"/>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A300" s="4"/>
       <c r="B300" s="4"/>
       <c r="C300" s="2"/>
@@ -5052,7 +5783,7 @@
       <c r="F300" s="2"/>
       <c r="G300" s="2"/>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A301" s="4"/>
       <c r="B301" s="4"/>
       <c r="C301" s="2"/>
@@ -5060,7 +5791,7 @@
       <c r="F301" s="2"/>
       <c r="G301" s="2"/>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A302" s="4"/>
       <c r="B302" s="4"/>
       <c r="C302" s="2"/>
@@ -5068,7 +5799,7 @@
       <c r="F302" s="2"/>
       <c r="G302" s="2"/>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A303" s="4"/>
       <c r="B303" s="4"/>
       <c r="C303" s="2"/>
@@ -5076,7 +5807,7 @@
       <c r="F303" s="2"/>
       <c r="G303" s="2"/>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A304" s="4"/>
       <c r="B304" s="4"/>
       <c r="C304" s="2"/>
@@ -5084,7 +5815,7 @@
       <c r="F304" s="2"/>
       <c r="G304" s="2"/>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A305" s="4"/>
       <c r="B305" s="4"/>
       <c r="C305" s="2"/>
@@ -5092,7 +5823,7 @@
       <c r="F305" s="2"/>
       <c r="G305" s="2"/>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="2"/>
@@ -5100,7 +5831,7 @@
       <c r="F306" s="2"/>
       <c r="G306" s="2"/>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="2"/>
@@ -5108,7 +5839,7 @@
       <c r="F307" s="2"/>
       <c r="G307" s="2"/>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="2"/>
@@ -5116,7 +5847,7 @@
       <c r="F308" s="2"/>
       <c r="G308" s="2"/>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="2"/>
@@ -5124,7 +5855,7 @@
       <c r="F309" s="2"/>
       <c r="G309" s="2"/>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="2"/>
@@ -5132,7 +5863,7 @@
       <c r="F310" s="2"/>
       <c r="G310" s="2"/>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="2"/>
@@ -5140,7 +5871,7 @@
       <c r="F311" s="2"/>
       <c r="G311" s="2"/>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A312" s="4"/>
       <c r="B312" s="4"/>
       <c r="C312" s="2"/>
@@ -5148,7 +5879,7 @@
       <c r="F312" s="2"/>
       <c r="G312" s="2"/>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="2"/>
@@ -5156,7 +5887,7 @@
       <c r="F313" s="2"/>
       <c r="G313" s="2"/>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="2"/>
@@ -5164,7 +5895,7 @@
       <c r="F314" s="2"/>
       <c r="G314" s="2"/>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="2"/>
@@ -5172,7 +5903,7 @@
       <c r="F315" s="2"/>
       <c r="G315" s="2"/>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="2"/>
@@ -5180,7 +5911,7 @@
       <c r="F316" s="2"/>
       <c r="G316" s="2"/>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="2"/>
@@ -5188,7 +5919,7 @@
       <c r="F317" s="2"/>
       <c r="G317" s="2"/>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="2"/>
@@ -5196,7 +5927,7 @@
       <c r="F318" s="2"/>
       <c r="G318" s="2"/>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A319" s="4"/>
       <c r="B319" s="4"/>
       <c r="C319" s="2"/>
@@ -5204,7 +5935,7 @@
       <c r="F319" s="2"/>
       <c r="G319" s="2"/>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A320" s="4"/>
       <c r="B320" s="4"/>
       <c r="C320" s="2"/>
@@ -5212,7 +5943,7 @@
       <c r="F320" s="2"/>
       <c r="G320" s="2"/>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A321" s="4"/>
       <c r="B321" s="4"/>
       <c r="C321" s="2"/>
@@ -5220,7 +5951,7 @@
       <c r="F321" s="2"/>
       <c r="G321" s="2"/>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A322" s="4"/>
       <c r="B322" s="4"/>
       <c r="C322" s="2"/>
@@ -5228,7 +5959,7 @@
       <c r="F322" s="2"/>
       <c r="G322" s="2"/>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A323" s="4"/>
       <c r="B323" s="4"/>
       <c r="C323" s="2"/>
@@ -5236,7 +5967,7 @@
       <c r="F323" s="2"/>
       <c r="G323" s="2"/>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A324" s="4"/>
       <c r="B324" s="4"/>
       <c r="C324" s="2"/>
@@ -5244,7 +5975,7 @@
       <c r="F324" s="2"/>
       <c r="G324" s="2"/>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="2"/>
@@ -5252,7 +5983,7 @@
       <c r="F325" s="2"/>
       <c r="G325" s="2"/>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="2"/>
@@ -5260,7 +5991,7 @@
       <c r="F326" s="2"/>
       <c r="G326" s="2"/>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="2"/>
@@ -5268,7 +5999,7 @@
       <c r="F327" s="2"/>
       <c r="G327" s="2"/>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="2"/>
@@ -5276,7 +6007,7 @@
       <c r="F328" s="2"/>
       <c r="G328" s="2"/>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A329" s="4"/>
       <c r="B329" s="4"/>
       <c r="C329" s="2"/>
@@ -5284,7 +6015,7 @@
       <c r="F329" s="2"/>
       <c r="G329" s="2"/>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A330" s="4"/>
       <c r="B330" s="4"/>
       <c r="C330" s="2"/>
@@ -5292,7 +6023,7 @@
       <c r="F330" s="2"/>
       <c r="G330" s="2"/>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A331" s="4"/>
       <c r="B331" s="4"/>
       <c r="C331" s="2"/>
@@ -5300,7 +6031,7 @@
       <c r="F331" s="2"/>
       <c r="G331" s="2"/>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A332" s="4"/>
       <c r="B332" s="4"/>
       <c r="C332" s="2"/>
@@ -5308,133 +6039,133 @@
       <c r="F332" s="2"/>
       <c r="G332" s="2"/>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A333" s="4"/>
       <c r="B333" s="4"/>
       <c r="C333" s="2"/>
       <c r="D333" s="2"/>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A334" s="4"/>
       <c r="B334" s="4"/>
       <c r="C334" s="2"/>
       <c r="D334" s="2"/>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A335" s="4"/>
       <c r="B335" s="4"/>
       <c r="C335" s="2"/>
       <c r="D335" s="2"/>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A336" s="4"/>
       <c r="B336" s="4"/>
       <c r="C336" s="2"/>
       <c r="D336" s="2"/>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A337" s="4"/>
       <c r="B337" s="4"/>
       <c r="C337" s="2"/>
       <c r="D337" s="2"/>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A338" s="4"/>
       <c r="B338" s="4"/>
       <c r="C338" s="2"/>
       <c r="D338" s="2"/>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A339" s="4"/>
       <c r="B339" s="4"/>
       <c r="C339" s="2"/>
       <c r="D339" s="2"/>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A340" s="4"/>
       <c r="B340" s="4"/>
       <c r="C340" s="2"/>
       <c r="D340" s="2"/>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A341" s="4"/>
       <c r="B341" s="4"/>
       <c r="C341" s="2"/>
       <c r="D341" s="2"/>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A342" s="4"/>
       <c r="B342" s="4"/>
       <c r="C342" s="2"/>
       <c r="D342" s="2"/>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A343" s="4"/>
       <c r="B343" s="4"/>
       <c r="C343" s="2"/>
       <c r="D343" s="2"/>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A344" s="4"/>
       <c r="B344" s="4"/>
       <c r="C344" s="2"/>
       <c r="D344" s="2"/>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A345" s="4"/>
       <c r="B345" s="4"/>
       <c r="C345" s="2"/>
       <c r="D345" s="2"/>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A346" s="4"/>
       <c r="B346" s="4"/>
       <c r="C346" s="2"/>
       <c r="D346" s="2"/>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A347" s="4"/>
       <c r="B347" s="4"/>
       <c r="C347" s="2"/>
       <c r="D347" s="2"/>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A348" s="4"/>
       <c r="B348" s="4"/>
       <c r="C348" s="2"/>
       <c r="D348" s="2"/>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A349" s="4"/>
       <c r="B349" s="4"/>
       <c r="C349" s="2"/>
       <c r="D349" s="2"/>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A350" s="4"/>
       <c r="B350" s="4"/>
       <c r="C350" s="2"/>
       <c r="D350" s="2"/>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A351" s="4"/>
       <c r="B351" s="4"/>
       <c r="C351" s="2"/>
       <c r="D351" s="2"/>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A352" s="4"/>
       <c r="B352" s="4"/>
       <c r="C352" s="2"/>
       <c r="D352" s="2"/>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="2"/>
       <c r="D353" s="2"/>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="2"/>
@@ -5455,30 +6186,30 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="6.05078125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.0234375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.76171875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.31640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.14453125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="11"/>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="23.25" x14ac:dyDescent="0.2">
+      <c r="A1" s="23"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -5488,7 +6219,7 @@
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -5498,7 +6229,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -5508,7 +6239,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -5518,7 +6249,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -5528,7 +6259,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -5538,7 +6269,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -5548,7 +6279,7 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -5558,7 +6289,7 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="6"/>
       <c r="C10" s="2"/>
@@ -5568,7 +6299,7 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -5578,7 +6309,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -5588,7 +6319,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -5598,7 +6329,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -5608,7 +6339,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -5618,7 +6349,7 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -5628,7 +6359,7 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -5638,7 +6369,7 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -5648,7 +6379,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -5658,7 +6389,7 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -5668,7 +6399,7 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -5678,7 +6409,7 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -5688,7 +6419,7 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -5698,7 +6429,7 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -5708,7 +6439,7 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -5718,7 +6449,7 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -5728,7 +6459,7 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -5738,7 +6469,7 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -5748,7 +6479,7 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -5758,7 +6489,7 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -5768,7 +6499,7 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
